--- a/artfynd/A 28059-2025 artfynd.xlsx
+++ b/artfynd/A 28059-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5675,6 +5675,302 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126135093</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sortmon, Sortmon, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>600831</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7027697</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126135229</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sortmon, Sortmon, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>600826</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7027809</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126135068</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sortmon, Sortmon, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>600815</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7027728</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28059-2025 artfynd.xlsx
+++ b/artfynd/A 28059-2025 artfynd.xlsx
@@ -5681,7 +5681,7 @@
         <v>126135093</v>
       </c>
       <c r="B45" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>126135068</v>
       </c>
       <c r="B47" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2025 artfynd.xlsx
+++ b/artfynd/A 28059-2025 artfynd.xlsx
@@ -5681,7 +5681,7 @@
         <v>126135093</v>
       </c>
       <c r="B45" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>126135068</v>
       </c>
       <c r="B47" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 28059-2025 artfynd.xlsx
+++ b/artfynd/A 28059-2025 artfynd.xlsx
@@ -5681,7 +5681,7 @@
         <v>126135093</v>
       </c>
       <c r="B45" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>126135068</v>
       </c>
       <c r="B47" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
